--- a/docs/Mech-Weapons.xlsx
+++ b/docs/Mech-Weapons.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FoundryData-Dev\Data\systems\mwd\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Apps\MWD-main\MWD\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FD2ABD-81A4-4D60-AA8F-6E01C5389A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71EB75E-FE7B-4A01-9A69-63729643ACF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{E1E4146D-AA47-4F02-8EE5-13D857F0DD65}"/>
+    <workbookView xWindow="5760" yWindow="1740" windowWidth="38700" windowHeight="15345" xr2:uid="{E1E4146D-AA47-4F02-8EE5-13D857F0DD65}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="106">
   <si>
     <t>Weapon</t>
   </si>
@@ -295,6 +295,66 @@
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>Tonnage/10</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Pilot REF</t>
+  </si>
+  <si>
+    <t>Sword</t>
+  </si>
+  <si>
+    <t>Axe</t>
+  </si>
+  <si>
+    <t>Katana</t>
+  </si>
+  <si>
+    <t>Claymore</t>
+  </si>
+  <si>
+    <t>BattleAxe</t>
+  </si>
+  <si>
+    <t>Arena Knuckles</t>
+  </si>
+  <si>
+    <t>Pilot REF -3</t>
+  </si>
+  <si>
+    <t>Pilot REF +3</t>
+  </si>
+  <si>
+    <t>(Tonnage/10) +1</t>
+  </si>
+  <si>
+    <t>(Tonnage/10) +2</t>
+  </si>
+  <si>
+    <t>(Tonnage/10) +3</t>
+  </si>
+  <si>
+    <t>Club (improvised)</t>
+  </si>
+  <si>
+    <t>Standard Melee</t>
+  </si>
+  <si>
+    <t>Battle Flail</t>
+  </si>
+  <si>
+    <t>Pilot REF -2</t>
+  </si>
+  <si>
+    <t>Pilot REF -4</t>
+  </si>
+  <si>
+    <t>(Tonnage/10) +4</t>
   </si>
 </sst>
 </file>
@@ -368,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -395,9 +455,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -737,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFC43064-AB08-4B2D-9CB9-2FA6A7A44140}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
@@ -745,6 +802,7 @@
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1837,19 +1895,19 @@
       <c r="A39" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="12" t="s">
         <v>46</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E39" s="5">
         <v>3</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="4">
         <v>0</v>
       </c>
       <c r="G39" s="4">
@@ -2049,7 +2107,9 @@
       <c r="D46" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E46" s="4"/>
+      <c r="E46" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -2066,9 +2126,11 @@
         <v>34</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E47" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
@@ -2087,14 +2149,278 @@
       <c r="D48" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E48" s="8"/>
+      <c r="E48" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="10">
+        <v>0</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E50" s="10">
+        <v>0</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" s="10">
+        <v>0</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="10">
+        <v>0</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" s="10">
+        <v>0</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" s="10">
+        <v>0</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E57" s="10">
+        <v>0</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/docs/Mech-Weapons.xlsx
+++ b/docs/Mech-Weapons.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FoundryData-Dev\Data\systems\mwd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FD2ABD-81A4-4D60-AA8F-6E01C5389A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1C50E4-E1FA-4AAE-952E-89FDD4021A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{E1E4146D-AA47-4F02-8EE5-13D857F0DD65}"/>
+    <workbookView xWindow="51480" yWindow="-4995" windowWidth="16440" windowHeight="28320" xr2:uid="{E1E4146D-AA47-4F02-8EE5-13D857F0DD65}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="104">
   <si>
     <t>Weapon</t>
   </si>
@@ -294,13 +294,70 @@
     <t>ER PPC (Clan)</t>
   </si>
   <si>
-    <t>6</t>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>0+3</t>
+  </si>
+  <si>
+    <t>Ultra Autocannon/10</t>
+  </si>
+  <si>
+    <t>LB Autocannon/10X</t>
+  </si>
+  <si>
+    <t>LB Autocannon/5X</t>
+  </si>
+  <si>
+    <t>Rotary Autocannon/5</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Ultra Autocannon/20</t>
+  </si>
+  <si>
+    <t>LB Autocannon/20X</t>
+  </si>
+  <si>
+    <t>0+12</t>
+  </si>
+  <si>
+    <t>0+21</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>0+6</t>
+  </si>
+  <si>
+    <t>2+4</t>
+  </si>
+  <si>
+    <t>-5</t>
+  </si>
+  <si>
+    <t>Heavy Gauss Rifle</t>
+  </si>
+  <si>
+    <t>Light Gauss Rifle</t>
+  </si>
+  <si>
+    <t>-3</t>
+  </si>
+  <si>
+    <t>ER Flamer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -338,7 +395,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -364,11 +421,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -391,18 +457,40 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -737,17 +825,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFC43064-AB08-4B2D-9CB9-2FA6A7A44140}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="12" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -772,389 +863,403 @@
       <c r="H1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="J1" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="9">
-        <v>0</v>
-      </c>
-      <c r="F2" s="8">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8">
-        <v>0</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="21">
+        <v>0</v>
+      </c>
+      <c r="F2" s="20">
+        <v>0</v>
+      </c>
+      <c r="G2" s="20">
+        <v>0</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="23">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="E3" s="21">
+        <v>0</v>
+      </c>
+      <c r="F3" s="20">
+        <v>0</v>
+      </c>
+      <c r="G3" s="20">
+        <v>0</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="23">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="E4" s="9">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
         <v>-5</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="8">
         <v>6</v>
       </c>
-      <c r="H4" s="4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="H4" s="8">
+        <v>0</v>
+      </c>
+      <c r="I4" s="13">
         <v>-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="J4" s="18">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="9">
         <v>1</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="8">
         <v>-5</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="8">
         <v>6</v>
       </c>
-      <c r="H5" s="4">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="13">
         <v>-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="J5" s="18">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="5">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8">
         <v>-2</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="8">
         <v>7</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="8">
         <v>4</v>
       </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="18">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="9">
         <v>1</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="8">
         <v>-5</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="8">
         <v>-1</v>
       </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4">
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13">
         <v>-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="J7" s="18">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="9">
-        <v>0</v>
-      </c>
-      <c r="F8" s="8">
+      <c r="E8" s="21">
+        <v>0</v>
+      </c>
+      <c r="F8" s="20">
         <v>-5</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="20">
         <v>-1</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="20">
         <v>-4</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="I8" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="23">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="C9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="8">
+      <c r="E9" s="21">
+        <v>0</v>
+      </c>
+      <c r="F9" s="20">
         <v>-5</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="20">
         <v>-1</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="20">
         <v>-4</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="I9" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="23">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="23">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23">
+        <v>275000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C12" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="5">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4">
-        <v>-1</v>
-      </c>
-      <c r="H10" s="4">
-        <v>-4</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="5">
-        <v>2</v>
-      </c>
-      <c r="F11" s="4">
-        <v>2</v>
-      </c>
-      <c r="G11" s="4">
-        <v>-1</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E12" s="9">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H12" s="8">
+        <v>-4</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="18">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>24</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="9"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="5">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>4</v>
-      </c>
-      <c r="G14" s="4">
-        <v>-1</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13" s="13"/>
+      <c r="J13" s="18">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="18">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E15" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="4">
         <v>-1</v>
@@ -1162,164 +1267,134 @@
       <c r="H15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="16">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="16">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="16">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="18">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="18">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="4">
-        <v>1</v>
-      </c>
-      <c r="F16" s="11">
-        <v>4</v>
-      </c>
-      <c r="G16" s="4">
-        <v>-1</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8">
-        <v>1</v>
-      </c>
-      <c r="H17" s="8">
-        <v>-6</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1</v>
-      </c>
-      <c r="F18" s="8">
-        <v>0</v>
-      </c>
-      <c r="G18" s="8">
-        <v>1</v>
-      </c>
-      <c r="H18" s="8">
-        <v>-6</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="9">
-        <v>2</v>
-      </c>
-      <c r="F19" s="8">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8">
-        <v>1</v>
-      </c>
-      <c r="H19" s="8">
-        <v>-6</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C20" s="8" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" s="9">
-        <v>2</v>
-      </c>
-      <c r="F20" s="8">
-        <v>0</v>
-      </c>
-      <c r="G20" s="8">
-        <v>1</v>
-      </c>
-      <c r="H20" s="8">
-        <v>-6</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="18">
+        <v>275000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>75</v>
@@ -1327,28 +1402,31 @@
       <c r="E21" s="5">
         <v>0</v>
       </c>
-      <c r="F21" s="4">
-        <v>-6</v>
-      </c>
-      <c r="G21" s="4">
-        <v>6</v>
-      </c>
-      <c r="H21" s="4">
-        <v>7</v>
-      </c>
-      <c r="I21" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="16">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>75</v>
@@ -1356,745 +1434,1078 @@
       <c r="E22" s="5">
         <v>1</v>
       </c>
-      <c r="F22" s="4">
-        <v>-6</v>
-      </c>
-      <c r="G22" s="4">
-        <v>6</v>
-      </c>
-      <c r="H22" s="4">
-        <v>7</v>
-      </c>
-      <c r="I22" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="17">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E23" s="5">
-        <v>2</v>
-      </c>
-      <c r="F23" s="4">
-        <v>-6</v>
-      </c>
-      <c r="G23" s="4">
-        <v>6</v>
-      </c>
-      <c r="H23" s="4">
-        <v>7</v>
-      </c>
-      <c r="I23" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="16">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="5">
-        <v>2</v>
-      </c>
-      <c r="F24" s="4">
-        <v>-6</v>
-      </c>
-      <c r="G24" s="4">
-        <v>6</v>
-      </c>
-      <c r="H24" s="4">
-        <v>7</v>
-      </c>
-      <c r="I24" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E24" s="9">
+        <v>0</v>
+      </c>
+      <c r="F24" s="8">
+        <v>0</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="18">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="E25" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="8">
         <v>0</v>
       </c>
-      <c r="G25" s="8">
-        <v>0</v>
+      <c r="G25" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J25" s="18">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="9">
+        <v>2</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="18">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="9">
+        <v>2</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="18">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="9">
-        <v>1</v>
-      </c>
-      <c r="F26" s="8">
-        <v>3</v>
-      </c>
-      <c r="G26" s="8">
-        <v>2</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="9">
-        <v>1</v>
-      </c>
-      <c r="F27" s="8">
-        <v>5</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="9">
-        <v>2</v>
-      </c>
-      <c r="F28" s="8">
-        <v>2</v>
-      </c>
-      <c r="G28" s="8">
-        <v>0</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C28" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4">
+        <v>-6</v>
+      </c>
+      <c r="G28" s="4">
+        <v>6</v>
+      </c>
+      <c r="H28" s="4">
+        <v>7</v>
+      </c>
+      <c r="I28" s="14">
+        <v>4</v>
+      </c>
+      <c r="J28" s="16">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="E29" s="5">
         <v>1</v>
       </c>
       <c r="F29" s="4">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="G29" s="4">
-        <v>-1</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="H29" s="4">
+        <v>7</v>
+      </c>
+      <c r="I29" s="14">
+        <v>4</v>
+      </c>
+      <c r="J29" s="16">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="E30" s="5">
         <v>2</v>
       </c>
       <c r="F30" s="4">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="G30" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H30" s="4">
-        <v>0</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" t="s">
-        <v>45</v>
+        <v>7</v>
+      </c>
+      <c r="I30" s="14">
+        <v>4</v>
+      </c>
+      <c r="J30" s="16">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="E31" s="5">
         <v>2</v>
       </c>
       <c r="F31" s="4">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="G31" s="4">
+        <v>6</v>
+      </c>
+      <c r="H31" s="4">
+        <v>7</v>
+      </c>
+      <c r="I31" s="14">
+        <v>4</v>
+      </c>
+      <c r="J31" s="16">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="8">
+        <v>0</v>
+      </c>
+      <c r="G32" s="8">
+        <v>0</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="18">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1</v>
+      </c>
+      <c r="F33" s="8">
+        <v>3</v>
+      </c>
+      <c r="G33" s="8">
         <v>2</v>
       </c>
-      <c r="H31" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="5">
-        <v>2</v>
-      </c>
-      <c r="F32" s="4">
-        <v>2</v>
-      </c>
-      <c r="G32" s="4">
-        <v>-1</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="9">
-        <v>2</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H33" s="8">
-        <v>-4</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>46</v>
+      <c r="H33" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="18">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E34" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="8">
         <v>5</v>
       </c>
       <c r="G34" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J34" s="18">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="9">
+        <v>2</v>
+      </c>
+      <c r="F35" s="8">
+        <v>2</v>
+      </c>
+      <c r="G35" s="8">
+        <v>0</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="18">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="5">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J36" s="16">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="5">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4">
+        <v>5</v>
+      </c>
+      <c r="G37" s="4">
+        <v>2</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J37" s="16">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="5">
+        <v>2</v>
+      </c>
+      <c r="F38" s="4">
+        <v>5</v>
+      </c>
+      <c r="G38" s="4">
+        <v>2</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J38" s="16">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="5">
+        <v>2</v>
+      </c>
+      <c r="F39" s="4">
+        <v>2</v>
+      </c>
+      <c r="G39" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J39" s="16">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="9">
+        <v>2</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G40" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H40" s="8">
+        <v>-4</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J40" s="18">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="9">
+        <v>3</v>
+      </c>
+      <c r="F41" s="8">
+        <v>5</v>
+      </c>
+      <c r="G41" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H41" s="8">
         <v>-2</v>
       </c>
-      <c r="I34" s="8">
+      <c r="I41" s="13">
         <v>-1</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="J41" s="18">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C42" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" s="9">
-        <v>3</v>
-      </c>
-      <c r="F35" s="8">
+      <c r="D42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="9">
+        <v>3</v>
+      </c>
+      <c r="F42" s="8">
         <v>5</v>
       </c>
-      <c r="G35" s="8">
-        <v>0</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="G42" s="8">
+        <v>0</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="18">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C43" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="9">
+      <c r="D43" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="9">
         <v>4</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F43" s="8">
         <v>4</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G43" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H43" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="I43" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="18">
+        <v>275000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C44" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="5">
-        <v>3</v>
-      </c>
-      <c r="F37" s="4">
+      <c r="D44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="5">
+        <v>3</v>
+      </c>
+      <c r="F44" s="4">
         <v>-9</v>
       </c>
-      <c r="G37" s="4">
-        <v>3</v>
-      </c>
-      <c r="H37" s="4">
-        <v>0</v>
-      </c>
-      <c r="I37" s="4">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="G44" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J44" s="16">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38" s="5">
-        <v>3</v>
-      </c>
-      <c r="F38" s="4">
-        <v>-4</v>
-      </c>
-      <c r="G38" s="4">
-        <v>3</v>
-      </c>
-      <c r="H38" s="4">
-        <v>1</v>
-      </c>
-      <c r="I38" s="4">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" s="5">
-        <v>3</v>
-      </c>
-      <c r="F39" s="12">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4">
-        <v>3</v>
-      </c>
-      <c r="H39" s="4">
-        <v>0</v>
-      </c>
-      <c r="I39" s="10">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E40" s="5">
-        <v>3</v>
-      </c>
-      <c r="F40" s="4">
-        <v>7</v>
-      </c>
-      <c r="G40" s="4">
-        <v>0</v>
-      </c>
-      <c r="H40" s="4">
-        <v>-7</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="5">
-        <v>3</v>
-      </c>
-      <c r="F41" s="4">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4">
-        <v>1</v>
-      </c>
-      <c r="H41" s="4">
-        <v>-2</v>
-      </c>
-      <c r="I41" s="4">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E42" s="5">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4">
-        <v>-9</v>
-      </c>
-      <c r="G42" s="4">
-        <v>3</v>
-      </c>
-      <c r="H42" s="4">
-        <v>0</v>
-      </c>
-      <c r="I42" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E43" s="5">
-        <v>4</v>
-      </c>
-      <c r="F43" s="4">
-        <v>-4</v>
-      </c>
-      <c r="G43" s="4">
-        <v>3</v>
-      </c>
-      <c r="H43" s="4">
-        <v>-2</v>
-      </c>
-      <c r="I43" s="4">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" s="9">
-        <v>1</v>
-      </c>
-      <c r="F44" s="8">
-        <v>2</v>
-      </c>
-      <c r="G44" s="8">
-        <v>0</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="5">
+        <v>3</v>
+      </c>
+      <c r="F45" s="4">
+        <v>-4</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" s="16">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="5">
+        <v>3</v>
+      </c>
+      <c r="F46" s="4">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I46" s="14">
+        <v>0</v>
+      </c>
+      <c r="J46" s="16">
+        <v>475000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="5">
+        <v>3</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="16">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="5">
+        <v>3</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" s="16">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="5">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4">
+        <v>-9</v>
+      </c>
+      <c r="G49" s="4">
+        <v>3</v>
+      </c>
+      <c r="H49" s="4">
+        <v>0</v>
+      </c>
+      <c r="I49" s="14">
+        <v>0</v>
+      </c>
+      <c r="J49" s="16">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="5">
+        <v>4</v>
+      </c>
+      <c r="F50" s="4">
+        <v>-4</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="14">
+        <v>-4</v>
+      </c>
+      <c r="J50" s="16">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="9">
+        <v>1</v>
+      </c>
+      <c r="F51" s="8">
+        <v>2</v>
+      </c>
+      <c r="G51" s="8">
+        <v>0</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J51" s="18">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="18">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E45" s="5">
-        <v>0</v>
-      </c>
-      <c r="F45" s="4">
+      <c r="E53" s="5">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4">
         <v>7</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G53" s="4">
         <v>2</v>
       </c>
-      <c r="H45" s="4">
+      <c r="H53" s="4">
         <v>-4</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="I53" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="4">
-        <v>3</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="C54" s="4">
+        <v>3</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C55" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D55" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I55" s="8"/>
+      <c r="J55" s="18"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C56" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D56" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I56" s="8"/>
+      <c r="J56" s="18"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/docs/Mech-Weapons.xlsx
+++ b/docs/Mech-Weapons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FoundryData-Dev\Data\systems\mwd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1C50E4-E1FA-4AAE-952E-89FDD4021A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85488DC7-86ED-4D29-BB1C-079C71C0743B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="-4995" windowWidth="16440" windowHeight="28320" xr2:uid="{E1E4146D-AA47-4F02-8EE5-13D857F0DD65}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="106">
   <si>
     <t>Weapon</t>
   </si>
@@ -349,6 +349,12 @@
   </si>
   <si>
     <t>ER Flamer</t>
+  </si>
+  <si>
+    <t>-10</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -356,7 +362,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -434,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -472,25 +478,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -871,66 +866,66 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="21">
-        <v>0</v>
-      </c>
-      <c r="F2" s="20">
-        <v>0</v>
-      </c>
-      <c r="G2" s="20">
-        <v>0</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="23">
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="16">
         <v>5000</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="21">
-        <v>0</v>
-      </c>
-      <c r="F3" s="20">
-        <v>0</v>
-      </c>
-      <c r="G3" s="20">
-        <v>0</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="23">
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="16">
         <v>11250</v>
       </c>
     </row>
@@ -1049,11 +1044,11 @@
       <c r="F7" s="8">
         <v>-5</v>
       </c>
-      <c r="G7" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="I7" s="13">
         <v>-2</v>
@@ -1063,110 +1058,110 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="21">
-        <v>0</v>
-      </c>
-      <c r="F8" s="20">
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
         <v>-5</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="4">
         <v>-1</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="4">
         <v>-4</v>
       </c>
-      <c r="I8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="23">
+      <c r="I8" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="16">
         <v>125000</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="21">
-        <v>0</v>
-      </c>
-      <c r="F9" s="20">
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
         <v>-5</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="4">
         <v>-1</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="4">
         <v>-4</v>
       </c>
-      <c r="I9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="23">
+      <c r="I9" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="16">
         <v>200000</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="20" t="s">
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="23">
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="16">
         <v>250000</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="20" t="s">
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="23">
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="16">
         <v>275000</v>
       </c>
     </row>
@@ -2135,11 +2130,11 @@
       <c r="D44" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E44" s="5">
-        <v>3</v>
-      </c>
-      <c r="F44" s="4">
-        <v>-9</v>
+      <c r="E44" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>27</v>
@@ -2170,17 +2165,17 @@
       <c r="E45" s="5">
         <v>3</v>
       </c>
-      <c r="F45" s="4">
-        <v>-4</v>
+      <c r="F45" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="G45" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I45" s="14" t="s">
         <v>52</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I45" s="14" t="s">
-        <v>24</v>
       </c>
       <c r="J45" s="16">
         <v>300000</v>
@@ -2206,13 +2201,13 @@
         <v>0</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I46" s="14">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>21</v>
       </c>
       <c r="J46" s="16">
         <v>475000</v>
@@ -2455,7 +2450,7 @@
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
-      <c r="H54" s="20" t="s">
+      <c r="H54" s="4" t="s">
         <v>102</v>
       </c>
       <c r="I54" s="4"/>

--- a/docs/Mech-Weapons.xlsx
+++ b/docs/Mech-Weapons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FoundryData-Dev\Data\systems\mwd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85488DC7-86ED-4D29-BB1C-079C71C0743B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF8D95C-22E4-4B96-9535-7587414E6B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="-4995" windowWidth="16440" windowHeight="28320" xr2:uid="{E1E4146D-AA47-4F02-8EE5-13D857F0DD65}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="110">
   <si>
     <t>Weapon</t>
   </si>
@@ -355,6 +355,18 @@
   </si>
   <si>
     <t>10</t>
+  </si>
+  <si>
+    <t>-8</t>
+  </si>
+  <si>
+    <t>-4</t>
+  </si>
+  <si>
+    <t>-6</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
 </sst>
 </file>
@@ -974,8 +986,8 @@
       <c r="D5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="9">
-        <v>1</v>
+      <c r="E5" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="F5" s="8">
         <v>-5</v>
@@ -1076,14 +1088,14 @@
       <c r="F8" s="4">
         <v>-5</v>
       </c>
-      <c r="G8" s="4">
-        <v>-1</v>
-      </c>
-      <c r="H8" s="4">
-        <v>-4</v>
+      <c r="G8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="J8" s="16">
         <v>125000</v>
@@ -1105,17 +1117,17 @@
       <c r="E9" s="5">
         <v>0</v>
       </c>
-      <c r="F9" s="4">
-        <v>-5</v>
-      </c>
-      <c r="G9" s="4">
-        <v>-1</v>
-      </c>
-      <c r="H9" s="4">
-        <v>-4</v>
+      <c r="F9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="J9" s="16">
         <v>200000</v>
@@ -1131,14 +1143,24 @@
       <c r="C10" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
+      <c r="D10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="F10" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="14"/>
+        <v>51</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="J10" s="16">
         <v>250000</v>
       </c>
@@ -1153,14 +1175,24 @@
       <c r="C11" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
+      <c r="D11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="F11" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="14"/>
+      <c r="G11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="J11" s="16">
         <v>275000</v>
       </c>
@@ -1181,14 +1213,14 @@
       <c r="E12" s="9">
         <v>1</v>
       </c>
-      <c r="F12" s="8">
-        <v>0</v>
-      </c>
-      <c r="G12" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H12" s="8">
-        <v>-4</v>
+      <c r="F12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>102</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>3</v>
@@ -1207,12 +1239,24 @@
       <c r="C13" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="13"/>
+      <c r="D13" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="J13" s="18">
         <v>320000</v>
       </c>
@@ -1227,12 +1271,24 @@
       <c r="C14" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="13"/>
+      <c r="D14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="J14" s="18">
         <v>400000</v>
       </c>
@@ -1253,11 +1309,11 @@
       <c r="E15" s="5">
         <v>2</v>
       </c>
-      <c r="F15" s="4">
-        <v>2</v>
-      </c>
-      <c r="G15" s="4">
-        <v>-1</v>
+      <c r="F15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>3</v>
@@ -1279,12 +1335,24 @@
       <c r="C16" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="14"/>
+      <c r="D16" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>3</v>
+      </c>
       <c r="J16" s="16">
         <v>480000</v>
       </c>
@@ -1299,12 +1367,24 @@
       <c r="C17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="14"/>
+      <c r="D17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>3</v>
+      </c>
       <c r="J17" s="16">
         <v>600000</v>
       </c>
@@ -1325,10 +1405,18 @@
       <c r="E18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="13"/>
+      <c r="F18" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="J18" s="18">
         <v>300000</v>
       </c>
@@ -1349,10 +1437,18 @@
       <c r="E19" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="13"/>
+      <c r="F19" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="J19" s="18">
         <v>500000</v>
       </c>
@@ -1373,10 +1469,18 @@
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="13"/>
+      <c r="F20" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="J20" s="18">
         <v>275000</v>
       </c>
@@ -1845,11 +1949,11 @@
       <c r="E35" s="9">
         <v>2</v>
       </c>
-      <c r="F35" s="8">
-        <v>2</v>
-      </c>
-      <c r="G35" s="8">
-        <v>0</v>
+      <c r="F35" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>3</v>
@@ -1909,14 +2013,14 @@
       <c r="E37" s="5">
         <v>2</v>
       </c>
-      <c r="F37" s="4">
-        <v>5</v>
-      </c>
-      <c r="G37" s="4">
-        <v>2</v>
-      </c>
-      <c r="H37" s="4">
-        <v>0</v>
+      <c r="F37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="I37" s="14" t="s">
         <v>3</v>
@@ -1941,11 +2045,11 @@
       <c r="E38" s="5">
         <v>2</v>
       </c>
-      <c r="F38" s="4">
-        <v>5</v>
-      </c>
-      <c r="G38" s="4">
-        <v>2</v>
+      <c r="F38" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>3</v>
@@ -1970,17 +2074,17 @@
       <c r="D39" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="5">
-        <v>2</v>
-      </c>
-      <c r="F39" s="4">
-        <v>2</v>
-      </c>
-      <c r="G39" s="4">
-        <v>-1</v>
+      <c r="E39" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I39" s="14" t="s">
         <v>3</v>
@@ -2037,17 +2141,17 @@
       <c r="E41" s="9">
         <v>3</v>
       </c>
-      <c r="F41" s="8">
-        <v>5</v>
+      <c r="F41" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="G41" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H41" s="8">
-        <v>-2</v>
-      </c>
-      <c r="I41" s="13">
-        <v>-1</v>
+      <c r="I41" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J41" s="18">
         <v>200000</v>
@@ -2069,14 +2173,14 @@
       <c r="E42" s="9">
         <v>3</v>
       </c>
-      <c r="F42" s="8">
-        <v>5</v>
-      </c>
-      <c r="G42" s="8">
-        <v>0</v>
+      <c r="F42" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I42" s="13" t="s">
         <v>3</v>
@@ -2101,17 +2205,17 @@
       <c r="E43" s="9">
         <v>4</v>
       </c>
-      <c r="F43" s="8">
-        <v>4</v>
+      <c r="F43" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="G43" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H43" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H43" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="I43" s="13" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="J43" s="18">
         <v>275000</v>

--- a/docs/Mech-Weapons.xlsx
+++ b/docs/Mech-Weapons.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FoundryData-Dev\Data\systems\mwd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF8D95C-22E4-4B96-9535-7587414E6B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2530D17-E0B6-4FD2-BBC8-0A1A54234572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="-4995" windowWidth="16440" windowHeight="28320" xr2:uid="{E1E4146D-AA47-4F02-8EE5-13D857F0DD65}"/>
+    <workbookView xWindow="27240" yWindow="1050" windowWidth="23205" windowHeight="19275" activeTab="1" xr2:uid="{E1E4146D-AA47-4F02-8EE5-13D857F0DD65}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Ranged" sheetId="1" r:id="rId1"/>
+    <sheet name="Melee" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="142">
   <si>
     <t>Weapon</t>
   </si>
@@ -165,9 +165,6 @@
     <t>Gauss Rifle</t>
   </si>
   <si>
-    <t>Heavy Assault Gauss</t>
-  </si>
-  <si>
     <t>Size</t>
   </si>
   <si>
@@ -288,9 +285,6 @@
     <t>Far</t>
   </si>
   <si>
-    <t xml:space="preserve"> Clan</t>
-  </si>
-  <si>
     <t>ER PPC (Clan)</t>
   </si>
   <si>
@@ -367,6 +361,108 @@
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>Size Slot</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Heat</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Standard Melee</t>
+  </si>
+  <si>
+    <t>Tonnage / 10</t>
+  </si>
+  <si>
+    <t>Pilot REF</t>
+  </si>
+  <si>
+    <t>Baseline unarmed strike / kick / punch</t>
+  </si>
+  <si>
+    <t>Arena Knuckles</t>
+  </si>
+  <si>
+    <t>Pilot REF +3</t>
+  </si>
+  <si>
+    <t>Precision striking weapon</t>
+  </si>
+  <si>
+    <t>Club (Improvised)</t>
+  </si>
+  <si>
+    <t>(Tonnage / 10) +1</t>
+  </si>
+  <si>
+    <t>Pilot REF -3</t>
+  </si>
+  <si>
+    <t>Cheap, clumsy impact weapon</t>
+  </si>
+  <si>
+    <t>Sword</t>
+  </si>
+  <si>
+    <t>Balanced cutting weapon</t>
+  </si>
+  <si>
+    <t>Axe</t>
+  </si>
+  <si>
+    <t>(Tonnage / 10) +2</t>
+  </si>
+  <si>
+    <t>Heavy chopping weapon</t>
+  </si>
+  <si>
+    <t>Katana</t>
+  </si>
+  <si>
+    <t>Precision blade focused on hit quality</t>
+  </si>
+  <si>
+    <t>Battle Flail</t>
+  </si>
+  <si>
+    <t>Pilot REF -2</t>
+  </si>
+  <si>
+    <t>Pilot REF -4</t>
+  </si>
+  <si>
+    <t>Can attack at Near range with additional penalty</t>
+  </si>
+  <si>
+    <t>Claymore</t>
+  </si>
+  <si>
+    <t>(Tonnage / 10) +3</t>
+  </si>
+  <si>
+    <t>Reliable heavy assault blade</t>
+  </si>
+  <si>
+    <t>BattleAxe</t>
+  </si>
+  <si>
+    <t>Brutal heavy cleaving weapon</t>
+  </si>
+  <si>
+    <t>Close AR</t>
+  </si>
+  <si>
+    <t>Near AR</t>
   </si>
 </sst>
 </file>
@@ -376,7 +472,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -397,6 +493,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="3">
@@ -452,7 +553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -498,6 +599,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,7 +944,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFC43064-AB08-4B2D-9CB9-2FA6A7A44140}">
   <dimension ref="A1:J57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" customWidth="1"/>
@@ -845,12 +956,12 @@
     <col min="10" max="10" width="12" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>36</v>
@@ -865,30 +976,30 @@
         <v>22</v>
       </c>
       <c r="G1" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="I1" s="12" t="s">
         <v>23</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2" s="5">
         <v>0</v>
@@ -909,18 +1020,18 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
@@ -941,18 +1052,18 @@
         <v>11250</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E4" s="9">
         <v>0</v>
@@ -973,18 +1084,18 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>24</v>
@@ -1005,18 +1116,18 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" s="9">
         <v>0</v>
@@ -1037,18 +1148,18 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" s="9">
         <v>1</v>
@@ -1069,18 +1180,18 @@
         <v>175000</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E8" s="5">
         <v>0</v>
@@ -1089,30 +1200,30 @@
         <v>-5</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J8" s="16">
         <v>125000</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" s="5">
         <v>0</v>
@@ -1124,33 +1235,33 @@
         <v>34</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J9" s="16">
         <v>200000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>27</v>
@@ -1159,56 +1270,56 @@
         <v>21</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J10" s="16">
         <v>250000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J11" s="16">
         <v>275000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E12" s="9">
         <v>1</v>
@@ -1220,7 +1331,7 @@
         <v>24</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>3</v>
@@ -1229,18 +1340,18 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>26</v>
@@ -1249,10 +1360,10 @@
         <v>24</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>3</v>
@@ -1261,18 +1372,18 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>25</v>
@@ -1293,18 +1404,18 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" s="5">
         <v>2</v>
@@ -1325,18 +1436,18 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>34</v>
@@ -1357,18 +1468,18 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="D17" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>26</v>
@@ -1377,7 +1488,7 @@
         <v>27</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>3</v>
@@ -1389,120 +1500,120 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J18" s="18">
         <v>300000</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J19" s="18">
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J20" s="18">
         <v>275000</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E21" s="5">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>24</v>
@@ -1517,24 +1628,24 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" s="5">
         <v>1</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>24</v>
@@ -1549,24 +1660,24 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" s="4">
         <v>1</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>24</v>
@@ -1581,18 +1692,18 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E24" s="9">
         <v>0</v>
@@ -1604,7 +1715,7 @@
         <v>21</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I24" s="13" t="s">
         <v>3</v>
@@ -1613,18 +1724,18 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" s="9">
         <v>1</v>
@@ -1636,7 +1747,7 @@
         <v>21</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>3</v>
@@ -1645,18 +1756,18 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E26" s="9">
         <v>2</v>
@@ -1668,7 +1779,7 @@
         <v>21</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I26" s="13" t="s">
         <v>3</v>
@@ -1677,18 +1788,18 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="E27" s="9">
         <v>2</v>
@@ -1700,7 +1811,7 @@
         <v>21</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>3</v>
@@ -1709,18 +1820,18 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E28" s="5">
         <v>0</v>
@@ -1741,18 +1852,18 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E29" s="5">
         <v>1</v>
@@ -1773,18 +1884,18 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E30" s="5">
         <v>2</v>
@@ -1805,18 +1916,18 @@
         <v>175000</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E31" s="5">
         <v>2</v>
@@ -1837,12 +1948,12 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>25</v>
@@ -1869,12 +1980,12 @@
         <v>11250</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>25</v>
@@ -1901,12 +2012,12 @@
         <v>11250</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>26</v>
@@ -1933,12 +2044,12 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>26</v>
@@ -1965,12 +2076,12 @@
         <v>31000</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="A36" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>26</v>
@@ -1997,12 +2108,12 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>26</v>
@@ -2029,12 +2140,12 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>34</v>
@@ -2061,12 +2172,12 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>34</v>
@@ -2093,12 +2204,12 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10">
       <c r="A40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>34</v>
@@ -2125,12 +2236,12 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10">
       <c r="A41" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>34</v>
@@ -2142,13 +2253,13 @@
         <v>3</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>24</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>24</v>
@@ -2157,12 +2268,12 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10">
       <c r="A42" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>21</v>
@@ -2174,7 +2285,7 @@
         <v>3</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>27</v>
@@ -2189,12 +2300,12 @@
         <v>175000</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10">
       <c r="A43" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>21</v>
@@ -2206,7 +2317,7 @@
         <v>4</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>27</v>
@@ -2215,18 +2326,18 @@
         <v>24</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J43" s="18">
         <v>275000</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>21</v>
@@ -2238,7 +2349,7 @@
         <v>26</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>27</v>
@@ -2253,12 +2364,12 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>21</v>
@@ -2270,30 +2381,30 @@
         <v>3</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J45" s="16">
         <v>300000</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>16</v>
@@ -2308,7 +2419,7 @@
         <v>27</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I46" s="14" t="s">
         <v>21</v>
@@ -2317,15 +2428,15 @@
         <v>475000</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>16</v>
@@ -2334,7 +2445,7 @@
         <v>3</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>27</v>
@@ -2349,12 +2460,12 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>21</v>
@@ -2369,7 +2480,7 @@
         <v>21</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>26</v>
@@ -2381,12 +2492,12 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>26</v>
@@ -2413,15 +2524,15 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10">
       <c r="A50" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>16</v>
@@ -2433,7 +2544,7 @@
         <v>-4</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>24</v>
@@ -2445,12 +2556,12 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>35</v>
@@ -2477,12 +2588,12 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>35</v>
@@ -2494,7 +2605,7 @@
         <v>25</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>34</v>
@@ -2509,18 +2620,18 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10">
       <c r="A53" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E53" s="5">
         <v>0</v>
@@ -2538,72 +2649,72 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10">
       <c r="A54" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C54" s="4">
         <v>3</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I54" s="4"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>34</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I55" s="8"/>
       <c r="J55" s="18"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I56" s="8"/>
       <c r="J56" s="18"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10">
       <c r="A57" s="1"/>
     </row>
   </sheetData>
@@ -2613,1283 +2724,275 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7460EB7-1132-45DC-8D09-54362426DF4A}">
-  <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2800A74-A09C-44E3-872D-CCC86CED39B3}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="35.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="22" customFormat="1">
+      <c r="A2" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="20">
+        <v>0</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="22" customFormat="1">
+      <c r="A3" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="20">
+        <v>0</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="22" customFormat="1">
+      <c r="A4" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C4" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="20">
+        <v>0</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="22" customFormat="1">
+      <c r="A5" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="20">
+        <v>0</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="22" customFormat="1">
+      <c r="A6" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="20">
+        <v>0</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="22" customFormat="1">
+      <c r="A7" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="20">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="22" customFormat="1">
+      <c r="A8" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="20">
+        <v>0</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="22" customFormat="1">
+      <c r="A9" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>-5</v>
-      </c>
-      <c r="G4">
-        <v>6</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>-5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>-2</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>-5</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C9" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="20">
+        <v>0</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="22" customFormat="1">
+      <c r="A10" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>-5</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-      <c r="H8">
-        <v>-4</v>
-      </c>
-      <c r="I8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>-5</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-      <c r="H9">
-        <v>-4</v>
-      </c>
-      <c r="I9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-      <c r="H10">
-        <v>-4</v>
-      </c>
-      <c r="I10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-      <c r="H11" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C10" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>4</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>4</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-      <c r="H15" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>4</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-      <c r="H16" t="s">
-        <v>3</v>
-      </c>
-      <c r="I16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>-6</v>
-      </c>
-      <c r="I17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>-6</v>
-      </c>
-      <c r="I18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>-6</v>
-      </c>
-      <c r="I19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>-6</v>
-      </c>
-      <c r="I20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>-6</v>
-      </c>
-      <c r="G21">
-        <v>6</v>
-      </c>
-      <c r="H21">
-        <v>7</v>
-      </c>
-      <c r="I21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>-6</v>
-      </c>
-      <c r="G22">
-        <v>6</v>
-      </c>
-      <c r="H22">
-        <v>7</v>
-      </c>
-      <c r="I22">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23">
-        <v>-6</v>
-      </c>
-      <c r="G23">
-        <v>6</v>
-      </c>
-      <c r="H23">
-        <v>7</v>
-      </c>
-      <c r="I23">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
-      <c r="F24">
-        <v>-6</v>
-      </c>
-      <c r="G24">
-        <v>6</v>
-      </c>
-      <c r="H24">
-        <v>7</v>
-      </c>
-      <c r="I24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25" t="s">
-        <v>3</v>
-      </c>
-      <c r="I25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-      <c r="H26" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>5</v>
-      </c>
-      <c r="G27" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
-      <c r="F28">
-        <v>2</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28" t="s">
-        <v>3</v>
-      </c>
-      <c r="I28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-      <c r="H29" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-      <c r="F30">
-        <v>5</v>
-      </c>
-      <c r="G30">
-        <v>2</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31">
-        <v>2</v>
-      </c>
-      <c r="F31">
-        <v>5</v>
-      </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
-      <c r="H31" t="s">
-        <v>3</v>
-      </c>
-      <c r="I31" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32">
-        <v>2</v>
-      </c>
-      <c r="F32">
-        <v>2</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-      <c r="H32" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33">
-        <v>2</v>
-      </c>
-      <c r="F33">
-        <v>4</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-      <c r="H33">
-        <v>-4</v>
-      </c>
-      <c r="I33" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34">
-        <v>3</v>
-      </c>
-      <c r="F34">
-        <v>5</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-      <c r="H34">
-        <v>-2</v>
-      </c>
-      <c r="I34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35">
-        <v>3</v>
-      </c>
-      <c r="F35">
-        <v>5</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36">
-        <v>4</v>
-      </c>
-      <c r="F36">
-        <v>4</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>-3</v>
-      </c>
-      <c r="I36" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>19</v>
-      </c>
-      <c r="B37" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37">
-        <v>3</v>
-      </c>
-      <c r="F37">
-        <v>-9</v>
-      </c>
-      <c r="G37">
-        <v>3</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>62</v>
-      </c>
-      <c r="B38" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38">
-        <v>3</v>
-      </c>
-      <c r="F38">
-        <v>-4</v>
-      </c>
-      <c r="G38">
-        <v>3</v>
-      </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>62</v>
-      </c>
-      <c r="B39" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" t="s">
-        <v>52</v>
-      </c>
-      <c r="E39" t="s">
-        <v>16</v>
-      </c>
-      <c r="F39">
-        <v>3</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>3</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" t="s">
-        <v>16</v>
-      </c>
-      <c r="E40">
-        <v>3</v>
-      </c>
-      <c r="F40">
-        <v>7</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>-7</v>
-      </c>
-      <c r="I40" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41">
-        <v>3</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <v>-2</v>
-      </c>
-      <c r="I41">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" t="s">
-        <v>45</v>
-      </c>
-      <c r="C42" t="s">
-        <v>26</v>
-      </c>
-      <c r="D42" t="s">
-        <v>16</v>
-      </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <v>-9</v>
-      </c>
-      <c r="G42">
-        <v>3</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" t="s">
-        <v>16</v>
-      </c>
-      <c r="E43">
-        <v>4</v>
-      </c>
-      <c r="F43">
-        <v>-4</v>
-      </c>
-      <c r="G43">
-        <v>3</v>
-      </c>
-      <c r="H43">
-        <v>-2</v>
-      </c>
-      <c r="I43">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" t="s">
-        <v>35</v>
-      </c>
-      <c r="D44" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" t="s">
-        <v>75</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>7</v>
-      </c>
-      <c r="G45">
-        <v>2</v>
-      </c>
-      <c r="H45">
-        <v>-4</v>
-      </c>
-      <c r="I45" t="s">
-        <v>3</v>
+      <c r="E10" s="20">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Mech-Weapons.xlsx
+++ b/docs/Mech-Weapons.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FoundryData-Dev\Data\systems\mwd\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2530D17-E0B6-4FD2-BBC8-0A1A54234572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A801808-DB6B-4394-8BFB-BFAF02577DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27240" yWindow="1050" windowWidth="23205" windowHeight="19275" activeTab="1" xr2:uid="{E1E4146D-AA47-4F02-8EE5-13D857F0DD65}"/>
+    <workbookView xWindow="27240" yWindow="1050" windowWidth="23205" windowHeight="19275" activeTab="2" xr2:uid="{E1E4146D-AA47-4F02-8EE5-13D857F0DD65}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranged" sheetId="1" r:id="rId1"/>
     <sheet name="Melee" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="145">
   <si>
     <t>Weapon</t>
   </si>
@@ -463,6 +464,15 @@
   </si>
   <si>
     <t>Near AR</t>
+  </si>
+  <si>
+    <t>(T / 10) +1</t>
+  </si>
+  <si>
+    <t>(T / 10) +2</t>
+  </si>
+  <si>
+    <t>(T / 10) +3</t>
   </si>
 </sst>
 </file>
@@ -472,7 +482,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -499,8 +509,16 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -513,8 +531,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -549,11 +573,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -608,7 +652,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2761,7 +2825,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="22" customFormat="1">
+    <row r="2" spans="1:8">
       <c r="A2" s="20" t="s">
         <v>113</v>
       </c>
@@ -2787,7 +2851,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="22" customFormat="1">
+    <row r="3" spans="1:8">
       <c r="A3" s="20" t="s">
         <v>117</v>
       </c>
@@ -2813,7 +2877,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="22" customFormat="1">
+    <row r="4" spans="1:8">
       <c r="A4" s="20" t="s">
         <v>120</v>
       </c>
@@ -2839,7 +2903,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="22" customFormat="1">
+    <row r="5" spans="1:8">
       <c r="A5" s="20" t="s">
         <v>124</v>
       </c>
@@ -2865,7 +2929,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="22" customFormat="1">
+    <row r="6" spans="1:8">
       <c r="A6" s="20" t="s">
         <v>126</v>
       </c>
@@ -2891,7 +2955,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="22" customFormat="1">
+    <row r="7" spans="1:8">
       <c r="A7" s="20" t="s">
         <v>129</v>
       </c>
@@ -2917,7 +2981,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="22" customFormat="1">
+    <row r="8" spans="1:8">
       <c r="A8" s="20" t="s">
         <v>131</v>
       </c>
@@ -2943,7 +3007,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="22" customFormat="1">
+    <row r="9" spans="1:8">
       <c r="A9" s="20" t="s">
         <v>135</v>
       </c>
@@ -2969,7 +3033,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="22" customFormat="1">
+    <row r="10" spans="1:8">
       <c r="A10" s="20" t="s">
         <v>138</v>
       </c>
@@ -2993,6 +3057,1791 @@
       </c>
       <c r="H10" s="20" t="s">
         <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E4B036-F522-4632-A41E-7B13ED894B12}">
+  <dimension ref="A1:I61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="25">
+        <v>0</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="25">
+        <v>0</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="25">
+        <v>0</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="25">
+        <v>0</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="25">
+        <v>0</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="25">
+        <v>0</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="25">
+        <v>0</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="25">
+        <v>0</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="25">
+        <v>0</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <v>-5</v>
+      </c>
+      <c r="G13" s="8">
+        <v>6</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="8">
+        <v>-5</v>
+      </c>
+      <c r="G14" s="8">
+        <v>6</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>-2</v>
+      </c>
+      <c r="G15" s="8">
+        <v>7</v>
+      </c>
+      <c r="H15" s="8">
+        <v>4</v>
+      </c>
+      <c r="I15" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8">
+        <v>-5</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="13">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4">
+        <v>-5</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="9">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="5">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="5">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="4">
+        <v>1</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1</v>
+      </c>
+      <c r="F34" s="8">
+        <v>0</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="9">
+        <v>2</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="9">
+        <v>2</v>
+      </c>
+      <c r="F36" s="8">
+        <v>0</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4">
+        <v>-6</v>
+      </c>
+      <c r="G37" s="4">
+        <v>6</v>
+      </c>
+      <c r="H37" s="4">
+        <v>7</v>
+      </c>
+      <c r="I37" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" s="5">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4">
+        <v>-6</v>
+      </c>
+      <c r="G38" s="4">
+        <v>6</v>
+      </c>
+      <c r="H38" s="4">
+        <v>7</v>
+      </c>
+      <c r="I38" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" s="5">
+        <v>2</v>
+      </c>
+      <c r="F39" s="4">
+        <v>-6</v>
+      </c>
+      <c r="G39" s="4">
+        <v>6</v>
+      </c>
+      <c r="H39" s="4">
+        <v>7</v>
+      </c>
+      <c r="I39" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="5">
+        <v>2</v>
+      </c>
+      <c r="F40" s="4">
+        <v>-6</v>
+      </c>
+      <c r="G40" s="4">
+        <v>6</v>
+      </c>
+      <c r="H40" s="4">
+        <v>7</v>
+      </c>
+      <c r="I40" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8">
+        <v>0</v>
+      </c>
+      <c r="G41" s="8">
+        <v>0</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="9">
+        <v>1</v>
+      </c>
+      <c r="F42" s="8">
+        <v>3</v>
+      </c>
+      <c r="G42" s="8">
+        <v>2</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1</v>
+      </c>
+      <c r="F43" s="8">
+        <v>5</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="9">
+        <v>2</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="5">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="5">
+        <v>2</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="5">
+        <v>2</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="9">
+        <v>2</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G49" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H49" s="8">
+        <v>-4</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="9">
+        <v>3</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="9">
+        <v>3</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="9">
+        <v>4</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="5">
+        <v>3</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="5">
+        <v>3</v>
+      </c>
+      <c r="F55" s="4">
+        <v>0</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="5">
+        <v>3</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="5">
+        <v>3</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="5">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4">
+        <v>-9</v>
+      </c>
+      <c r="G58" s="4">
+        <v>3</v>
+      </c>
+      <c r="H58" s="4">
+        <v>0</v>
+      </c>
+      <c r="I58" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="5">
+        <v>4</v>
+      </c>
+      <c r="F59" s="4">
+        <v>-4</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I59" s="14">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="9">
+        <v>1</v>
+      </c>
+      <c r="F60" s="8">
+        <v>2</v>
+      </c>
+      <c r="G60" s="8">
+        <v>0</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I61" s="13" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
